--- a/Result/profitability/2072.xlsx
+++ b/Result/profitability/2072.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM20"/>
+  <dimension ref="A1:AM21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2954,6 +2954,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4898</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3887</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1011</v>
+      </c>
+      <c r="F21" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="G21" t="n">
+        <v>922</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>18.83%</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>58</v>
+      </c>
+      <c r="J21" t="n">
+        <v>980</v>
+      </c>
+      <c r="K21" t="n">
+        <v>788</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N21" t="n">
+        <v>25.43125</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-1.149999999999999</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.2186311787072243</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-10.28</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.3324708926261319</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.5110294117647058</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-4.419999999999998</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-0.1763766959297685</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK21" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
